--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU_05/HRM/post DFS_HRM-2031-0212/Panel 7/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU05_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU_05/HRM/post DFS_HRM-2031-0212/Panel 7/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU05_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.01158</v>
+        <v>17.18436</v>
       </c>
       <c r="D2" t="n">
-        <v>17.04975</v>
+        <v>16.64116</v>
       </c>
       <c r="E2" t="n">
-        <v>17.26116</v>
+        <v>17.1415</v>
       </c>
       <c r="F2" t="n">
-        <v>43.14172</v>
+        <v>43.05482</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05257</v>
+        <v>0.05128</v>
       </c>
       <c r="H2" t="n">
-        <v>1.83553</v>
+        <v>1.79815</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.43259</v>
+        <v>17.27737</v>
       </c>
       <c r="D3" t="n">
-        <v>16.87276</v>
+        <v>16.47421</v>
       </c>
       <c r="E3" t="n">
-        <v>16.91509</v>
+        <v>17.04042</v>
       </c>
       <c r="F3" t="n">
-        <v>42.97995</v>
+        <v>43.36946</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05311</v>
+        <v>0.0515</v>
       </c>
       <c r="H3" t="n">
-        <v>1.85091</v>
+        <v>1.87543</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.86444</v>
+        <v>17.20332</v>
       </c>
       <c r="D4" t="n">
-        <v>16.70972</v>
+        <v>16.86397</v>
       </c>
       <c r="E4" t="n">
-        <v>16.63073</v>
+        <v>17.0373</v>
       </c>
       <c r="F4" t="n">
-        <v>43.036</v>
+        <v>43.38474</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05107</v>
+        <v>0.05201</v>
       </c>
       <c r="H4" t="n">
-        <v>1.84578</v>
+        <v>1.87947</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.1398</v>
+        <v>16.89989</v>
       </c>
       <c r="D6" t="n">
-        <v>16.03817</v>
+        <v>16.19659</v>
       </c>
       <c r="E6" t="n">
-        <v>16.92131</v>
+        <v>16.62471</v>
       </c>
       <c r="F6" t="n">
-        <v>21.92523</v>
+        <v>22.46447</v>
       </c>
       <c r="G6" t="n">
-        <v>35.14539</v>
+        <v>35.18746</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.66974</v>
+        <v>16.85573</v>
       </c>
       <c r="D7" t="n">
-        <v>16.52189</v>
+        <v>16.02684</v>
       </c>
       <c r="E7" t="n">
-        <v>16.24185</v>
+        <v>16.78113</v>
       </c>
       <c r="F7" t="n">
-        <v>22.48694</v>
+        <v>22.04474</v>
       </c>
       <c r="G7" t="n">
-        <v>35.0601</v>
+        <v>34.68399</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.82671</v>
+        <v>16.61566</v>
       </c>
       <c r="D8" t="n">
-        <v>16.12572</v>
+        <v>16.07239</v>
       </c>
       <c r="E8" t="n">
-        <v>16.69526</v>
+        <v>16.57343</v>
       </c>
       <c r="F8" t="n">
-        <v>22.01116</v>
+        <v>22.12452</v>
       </c>
       <c r="G8" t="n">
-        <v>35.1517</v>
+        <v>35.07616</v>
       </c>
     </row>
   </sheetData>
